--- a/Combined_Broker_Trades_with_ISIN.xlsx
+++ b/Combined_Broker_Trades_with_ISIN.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2" documentId="11_0B4E91BF92AC475D621755CB58CF2275F418AE48" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BE80D0C-84A6-450D-8876-C1F3FCD82340}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2535" yWindow="3420" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
